--- a/2022 data/excel_outputs/358_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/358_boothwise_data.xlsx
@@ -14,483 +14,1329 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="461">
   <si>
     <t>AC 358 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0 ##0 ###### ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ###### ;########ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ############# ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ############ ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## #### ###### ######## ########</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########## ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ### ### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;###0##ddh</t>
-  </si>
-  <si>
-    <t>##0 ##### ######## ######### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##### ######## ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ### ##.1 ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ### ##.1 ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ### ##.1;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #########</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #####</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##########</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ### #####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #######</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ########## ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ########## ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #######</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ##### ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ##### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## #### ######;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######</t>
-  </si>
-  <si>
-    <t>######## ######## #####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####### #### ### ##### ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####### #### ### ##### ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###########</t>
-  </si>
-  <si>
-    <t>######## ######## #######</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### ### ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### ### ### ;#0ddh</t>
-  </si>
-  <si>
-    <t>### #### ### #### ##### ##### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>### #### ### #### ##### ##### #### ;##ddh</t>
-  </si>
-  <si>
-    <t>### #### ### #### ##### ##### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##### ########### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##### ########### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######### ##### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######### ##### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ;###0##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## #### ;###0#0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ## #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ## #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ;####### ###ddh</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ########</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##########</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### #######</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0 #####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0.2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### ####### ;########ddh</t>
-  </si>
-  <si>
-    <t>##0 ##### ##### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##### ##### ##### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ;#0 ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ;#########ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ;###0####.1ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ;#0 ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ;#####ddh ######### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ;#####ddh ######### ;#0 ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ###</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## #### ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ### ;##0 ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ### ;#0 ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########## ;##0 ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########## ;#0 ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### ## #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ####</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ##### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0.1 ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##0.1 ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #### ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #### ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##### ##### ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ##### ####### ;##ddh</t>
-  </si>
-  <si>
-    <t>##### ##### ####### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ;#######ddh ### ## ###</t>
-  </si>
-  <si>
-    <t>####### #0 ##0 ##0 ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>#0 ##0 ######## ######### ;####ddh ;##0ddh</t>
-  </si>
-  <si>
-    <t>#0 ##0 ######## ######### ;####ddh ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 ######### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 ######### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### ;##### ## ####ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ######## ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ########### ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ########### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ######</t>
-  </si>
-  <si>
-    <t>######## ######## ####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ;#0ddh</t>
-  </si>
-  <si>
-    <t>### ####0 ##0 ###### ####</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 ###### ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ####0 ##0 ###### ;#0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##.# ;##0ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##.# ;#0ddh</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ;##ddh</t>
-  </si>
-  <si>
-    <t>####0 #### ######## ### ;##0ddh</t>
-  </si>
-  <si>
-    <t>####0 #### ######## ### ;#0ddh</t>
+    <t>BBHCHABBH|CH DYASHR|J|DACH|AI|AI|CH SHRCH|DAJ|NDACH|SHR|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH DYASHR|J|DACH|AI|AI|CH SHRCH|DAJ|NDACH|SHR|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH DYASHR|J|DACH|AI|AI|CH SHRCH|DAJ|NDACH|SHR|D YAI|CH|SHR|SHR|CH|BBH|CH|J|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN JMTAHAMNASAP</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH|DACHK|CHCHABBH|CHK|CHAK|SHRCHADYATHATHABHDYABBHDYASHR L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH|DACHK|CHCHABBH|CHK|CHAK|SHRCHADYATHATHABHDYABBHDYASHR L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN AIMIMIMSACHANAT</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHT|BBHDYAIDYASHRADYAK|CHK|BBHDYASHRCHADYAK|SHRADYATHATHABHDYABBHDYASHR L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRCH|KDYAK|SHRCH|CHBBHDYAIDYAK L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRCH|KDYAK|SHRCH|CHBBHDYAIDYAK L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>TMUSAMOIMD AIPADAHI THAMSAPAM TAPAKALAMSAMLAM AIMTAMLABIMUMJ</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH THATHABHK|J~NADYASHRCHADYAKDYAIDYATHATHABHDYABBHDYASHR L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH THATHABHK|J~NADYASHRCHADYAKDYAIDYATHATHABHDYABBHDYASHR L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCHAPDAJ|CH|DAN YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBH|CHK|SHRADYABBHDYAK|CH L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCHAPDAJ|CH|DAN YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH|BHP |PTHAPT|T|AI BBH|DAN JBHPDANDAK SHRCHAPDAJ|CH|DAN</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH DYASHRAPCH|AI|D Y DADAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH KL|AIBHT|CHBBHDY|PDYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH DYASHRAPCH|AI|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH SHRATHABHDYAK|DABBHDYAJBH SHRADYABBHDYASHRCHADYAIDYAK|PDYAK|AIDYAK KL|AIBHT|CHBBHDY|PDYAK|THATHABHDYABBHDYASHRADYAK L K|K|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH SHRATHABHDYAK|DABBHDYAJBH SHRADYABBHDYASHRCHADYAIDYAK|PDYAK|AIDYAK KL|AIBHT|CHBBHDY|PDYAK|THATHABHDYABBHDYASHRADYAK|L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCHMNDAJ SHRCH|DAI|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCHMNDAJ SHRCH|DAI|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>SHRCH|DAK|S|D BBHCHABBH|CH |PCHMNDAJ SHRCH|DAI|D Y DADAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>SHRCH|DAK|S|D BBHCHABBH|CH |PCHMNDAJ SHRCH|DAI|D Y NBDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBHDYAJDYASHRCHADYAK|BBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBHDYAJDYASHRCHADYAK|BBH L K|K|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN TMHINADAMJICHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JD|CH|DAK|DAMCH|J|BBH|CH|J YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JD|CH|DAK|DAMCH|J|BBH|CH|J Y DADAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN NTAMPADAP</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCHAPDACH|J|DAK|CHMBBHPCH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCHAPDACH|J|DAK|CHMBBHPCH Y DADAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBH|CHK|J~NACHAK|SHR THATHABHDYAK|CHAK|SHRCHADYAK L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBH|CHK|J~NACHAK|SHR THATHABHDYAK|CHAK|SHRCHADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBH|CHK|J~NACHAK|SHR THATHABHDYAK|CHAK|SHRCHADYAK L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THABHDAMDAK|BBH|CH|J YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THABHDAMDAK|BBH|CH|J YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH JBH|THABHK|DAK|J~NADYATHATHABHDYABBHDYASHR L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCH|AI|SHR|DAK|BBH|CH|J YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCH|AI|SHR|DAK|BBH|CH|J YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMIMEMT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCHAPDAJ|CH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCHAPDAJ|CH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH JBH|THABHBBHDYATHABHCH DYACHJBH|CHJDYAJDY|P |PTHABHJDYABBHDYASHRCHADYAK|J~NADYATHATHABHDYABBHDYASHR L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH JBH|THABHBBHDYATHABHCH DYACHJBH|CHJDYAJDY|P |PTHABHJDYABBHDYASHRCHADYAK|J~NADYATHATHABHDYABBHDYASHR L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRATHABHDYAK|SHRCHADYAK|DAK|SHRADYAK DYACHK|PDYAKDYACHATHATHABHDYABBHDYASHR L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRATHABHDYAK|SHRCHADYAK|DAK|SHRADYAK DYACHK|PDYAKDYACHATHATHABHDYABBHDYASHR L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN BIIPAJANACHAMSAP</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THAPD|DAJ|D SHRCH|T|AIPCH|D Y BBH|T|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THAPD|DAJ|D SHRCH|T|AIPCH|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMAMTAP BHMTAMAI THAMEMDAMJ</t>
+  </si>
+  <si>
+    <t>CHNCHAN KMDAKAMTAP SMAINEMTAML</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHPACHAMTAMCHAMJAJAP</t>
+  </si>
+  <si>
+    <t>CHNCHAN THAMIVATAMCHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN TAPATAMIIMJAP</t>
+  </si>
+  <si>
+    <t>CHNCHANPADAKAMTACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHANJAMAIM</t>
+  </si>
+  <si>
+    <t>CHNCHANCHAMDAKAMALACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CHAMDANDAK YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CHAMDANDAK YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH|DAK|CHAK|J~N L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CHAMDANDAK YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN THIMTAJIPACHANAT</t>
+  </si>
+  <si>
+    <t>THATHABHDYAKDYABBHDYAJ~N KL|SHRCHADYAK|SHRADACH SHRADYABBHDYASHRCHADYAIDYAK|PDYAK|AIDYAK BBHDAK|SHRADYABBH DYACHK|PDYAKDYACHATHATHABHDYABBHDYASHR L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHDYAKDYABBHDYAJ~N KL|SHRCHADYAK|SHRADACH SHRADYABBHDYASHRCHADYAIDYAK|PDYAK|AIDYAK BBHDAK|SHRADYABBH DYACHK|PDYAKDYACHATHATHABHDYABBHDYASHR L|CHABBHDYASHRCHADYASHRCHADY|PDYAK</t>
+  </si>
+  <si>
+    <t>THATHABHDYAKDYABBHDYAJ~N KL|SHRCHADYAK|SHRADACH SHRADYABBHDYASHRCHADYAIDYAK|PDYAK|AIDYAK BBHDAK|SHRADYABBH DYACHK|PDYAKDYACHATHATHABHDYABBHDYASHR L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN KMIMTAP AIIMDAMTACHANAT</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH DYACHK|SHRADYAK|AIDYAK SHRATHABHDYAK|THABHDYASHRCHADYAK|BBHDYASHRADYAK L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH DYACHK|SHRADYAK|AIDYAK SHRATHABHDYAK|THABHDYASHRCHADYAK|BBHDYASHRADYAK L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JBH|DAJ|J|D|PT|TP YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JBH|DAJ|J|D|PT|TP YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN TMUCHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHANUMRIMNUM</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DASHRAPCH|DAI|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DASHRAPCH|DAI|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHAMTAMBII</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THAPPCH|PCH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH JBH|CHCHBBHDYACHBBH L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THAPPCH|PCH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAMSAMNASAP</t>
+  </si>
+  <si>
+    <t>CHNCHANCHAMTAMEPALAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN THAMSANUM</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMAIMDACHANATAM</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PPDAK|DAJ|BBH|CH|J J|CHMPCH|K|BBH|CH|J|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCH|DAJ|CH|S|D SHRCH|DAI|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH DYACHBBHDYAK|SHRADYABBHDYAIDYAK AIBHTBBHDYAK|PDYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCH|DAJ|CH|S|D SHRCH|DAI|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCH|DAJ|CH|S|D SHRCH|DAI|D YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCH|DAJ|CH|S|D SHRCH|DAI|D YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH DYACHBBHDYAK|SHRADYABBHDYAIDYAK AIBHTBBH|CHBBHDYASHRADYASHRCH L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH DYACHBBHDYAK|SHRADYABBHDYAIDYAK AIBHTBBH|CHBBHDYASHRADYASHRCH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JBH|DAI|DAMDAJ|D BBH|DAN JBHPDANDAK YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRATHABHDYAK|PDYAK|DAK|SHRADYAK THATHABHDYAK|CH SHRATHABHCHK|CHAK|J~N L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JBH|DAI|DAMDAJ|D BBH|DAN JBHPDANDAK YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMSAJAM</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|CH|CH|J|DAPD</t>
+  </si>
+  <si>
+    <t>CHNCHAN JINAUIMUVIMD</t>
+  </si>
+  <si>
+    <t>CHNCHAN |AVASIP</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH DYAMDAKNDAJ YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH DYAMDAKNDAJ YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH |PTHAPT|T|AI AIBHT|DAN YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH |PTHAPT|T|AI AIBHT|DAN YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>|PPJ|CH|K|DASHRAP JBH|DAPD THABHCH|BHP |PTHAPT|T|AI AIBHT|DAN YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>|PPJ|CH|K|DASHRAP JBH|DAPD THABHCH|BHP |PTHAPT|T|AI AIBHT|DAN YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH DYACHBBHDACHAK|SHR AIBHTBBH|CHBBHDYASHRADYASHRCH L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH DYACHBBHDACHAK|SHR AIBHTBBH|CHBBHDYASHRADYASHRCH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN AINASAJAMDAPACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN TMHIVACHANAT</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBH|CHK|SHRCHADYAK|DAK|SHRADYAK L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBH|CHK|SHRCHADYAK|DAK|SHRADYAK L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH K|DAPJ|DAT|BBH|CH|J YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH K|DAPJ|DAT|BBH|CH|J YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHAMEMTAMJ CHNAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN TMNATAMBIMUMT</t>
+  </si>
+  <si>
+    <t>CHNCHAN AIMTAMLAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN JIMTAPUMJ</t>
+  </si>
+  <si>
+    <t>BBH|BBH|CHABBHDYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|CHACHK|SHR THATHABHK|AIBHTDYAIBHTDYABBH THATHABHDYAJDYASHRADYAIBHT|CH L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBH|BBH|CHABBHDYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|CHACHK|SHR THATHABHK|AIBHTDYAIBHTDYABBH THATHABHDYAJDYASHRADYAIBHT|CH L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBH|BBH|CHABBHDYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|CHACHK|SHR THATHABHK|AIBHTDYAIBHTDYABBH THATHABHDYAJDYASHRADYAIBHT|CH L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH J~NADYAK|J~NADYASHRCHADYAK L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH J~NADYAK|J~NADYASHRCHADYAK L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH |PTHAPT|T|AI THAPPCH|SHR|DACH|K|CH BBH|DAN JBHPDANDAK YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH |PTHAPT|T|AI THAPPCH|SHR|DACH|K|CH BBH|DAN JBHPDANDAK YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH |PTHAPT|T|AI THAPPCH|SHR|DACH|K|CH BBH|DAN JBHPDANDAK YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH |PTHAPT|T|AI THAPPCH|SHR|DACH|K|CH BBH|DAN JBHPDANDAK YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>KL|CHAK|SHR DYACHCHK|CHBBHDYASHRCH SHRATHABHCHK|THABHDYAK|AIBHT DYACHBBHDYAJ~NADYATHABHCH BBHBBH JBH|BBH SHRAK|DAK|SHRADYAK L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>KL|CHAK|SHR DYACHCHK|CHBBHDYASHRCH SHRATHABHCHK|THABHDYAK|AIBHT DYACHBBHDYAJ~NADYATHABHCH BBHBBH JBH|BBH SHRAK|DAK|SHRADYAK L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>KL|CHAK|SHR DYACHCHK|CHBBHDYASHRCH SHRATHABHCHK|THABHDYAK|AIBHT DYACHBBHDYAJ~NADYATHABHCH BBHBBH JBH|BBH SHRAK|DAK|SHRADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>KL|CHAK|SHR DYACHCHK|CHBBHDYASHRCH SHRATHABHCHK|THABHDYAK|AIBHT DYACHBBHDYAJ~NADYATHABHCH BBHBBH JBH|BBH SHRAK|DAK|SHRADYAK L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>KL|CHAK|SHR DYACHCHK|CHBBHDYASHRCH SHRATHABHCHK|THABHDYAK|AIBHT DYACHBBHDYAJ~NADYATHABHCH BBHBBH JBH|BBH SHRAK|DAK|SHRADYAK L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>J~NADYAK|AIBHT|CHBBHDYASHRADYAK J~NADYAK|CHKDYABBHDYASHRCH|CHAIDYAK|PDYAK|AI SHRAK|DAK|SHRADYAK L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>J~NADYAK|AIBHT|CHBBHDYASHRADYAK J~NADYAK|CHKDYABBHDYASHRCH|CHAIDYAK|PDYAK|AI SHRAK|DAK|SHRADYAK L|J~NADYAJDYASHRADYAIBHT|CHDACHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>J~NADYAK|AIBHT|CHBBHDYASHRADYAK J~NADYAK|CHKDYABBHDYASHRCH|CHAIDYAK|PDYAK|AI SHRAK|DAK|SHRADYAK L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>J~NADYAK|AIBHT|CHBBHDYASHRADYAK J~NADYAK|CHKDYABBHDYASHRCH|CHAIDYAK|PDYAK|AI SHRAK|DAK|SHRADYAK L|DAJDYABBHDYAIBHT|CHDACHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHMAI|DANCH|S|D |PTHAPT|T|AI JDAMDAJ|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHD|PDYAK|CHABBHDYAIDYAK DYACHJBH|CHJDYAJDY|P SHRAK|DAK|SHRADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHMAI|DANCH|S|D |PTHAPT|T|AI JDAMDAJ|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH |PTHAPT|T|AI JDAMDAJ|D YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH JBH|THABHBBH DYACHJBH|CHJDYAJDY|P SHRAK|DAK|SHRADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>AIBHT|CH THABHCH |PTHAPT|T|AI JDAMDAJ|D YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JDAMDAJ|D YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRAK|DAK|SHRADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JDAMDAJ|D YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>THABHDAJ|CH|T|DAK BBHCHABBH|CH JDAMDAJ|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>JBH|THABHK|SHRADYABBHDYAJDYAK|J~N THATHABHBBH|THATHABHDYABBH SHRAK|DAK|SHRADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THABHDAJ|CH|T|DAK BBHCHABBH|CH JDAMDAJ|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THABHCH|SHR|D SHRCH|D BBHCH|J|D</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH DYAPCH|J|BBH|CH|J|D Y|T|SHRANDAJ|CH K|T|J|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHTBBHDYAK|J~NADYAIDYAK THATHABHBBH|THATHABHDYABBH AIDYAK|SHRCH|CHBBHDYAIDYAK L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>AIBHTBBHDYAK|J~NADYAIDYAK THATHABHBBH|THATHABHDYABBH AIDYAK|SHRCH|CHBBHDYAIDYAK L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DASHR|DAPCH|J|D</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHNATAM KMSAMP JPUMTAP</t>
+  </si>
+  <si>
+    <t>CHNCHAN |AIMDACHANATAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHAMEPATACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN TNACHAMTAMACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DAJ|DAS|DAK|BBH|CH|J YATHAPPCH|SHR|DAKPDAJ|DAKKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAVAMSAVACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBHDAJ|DAMCH|S|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH THATHABHK|SHRADYAK|DABBHDYAIDYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI |PCH|AI|CH|CH YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI |PCH|AI|CH|CH YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DANSHR|DACH|AI|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DANSHR|DACH|AI|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>SHRANIN AIBIVAVAS AINASAJAMDACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCH|AI|SHR|DAK|BBH|CH|J YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PCH|AI|SHR|DAK|BBH|CH|J YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN |IIMDACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMBIUMT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH AIBHT|DANDAI|BBH|CH|J CHAJ PSHRCHAPDAJ|DABH|BBH|CH|J|D</t>
+  </si>
+  <si>
+    <t>CHNCHAN TMRAUMSACHANAT DAN0 CHMBIUMT</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH JBH|CHK|J~NADYASHRCHADYASHRADYAK|CHAK|SHR SHRCH|BBHDYATHABHDYAK|BBHDY|PDYABBH L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH JBH|CHK|J~NADYASHRCHADYASHRADYAK|CHAK|SHR SHRCH|BBHDYATHABHDYAK|BBHDY|PDYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN AIIMIIMRACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN TMEVAVASACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DACH|AI|CH|BBH|DAI|CH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMJAMDAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAMKIVACHANAT CHAVAN 2</t>
+  </si>
+  <si>
+    <t>CHNCHAN TMRAMUMSACHANAT NT ICHAMUMCHANATAM</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRAK|JDYAK|CHAK|PDYATHATHABHDYABBHDYASHR BBH|SHR CHTHATHABHDYAK|CHAK|THATHABHDYABBHDYASHRADYAK L|PDYAK|CHBBHDYASHRADYAK|SHRCHADYABBHCHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAMIMJUMT</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHAMKAMNASAP</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|CHAMPDAPD JBH|CH|T|CH|J|DABH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH SHRATHABHDYAK|DABBHDYAJBH DYACHJBH|CHJDYAJDY|P AIBHTBBH|CHK|SHRCHADYAK|DAK|SHRADYAK</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DAJ|DAK|CH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DAJ|DAK|CH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN AIMDAKAMSACHANAT</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI |PDAJ|DAS|PPDAJ|SHR|CH YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI |PDAJ|DAS|PPDAJ|SHR|CH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH J~NADYAK|SHRCHADYAK|SHRADYABBH L|CHAK|J~NADYASHRCHADYAK|BBH J~NAJ~NATHABH DYACHK|SHRADYAK|AIDYACHCHK|SHRADYAIBHTDYABBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PDAJ|DAS|PPDAJ|SHR|CH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PDAJ|DAS|PPDAJ|SHR|CH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH DYASHR|DAJMCHAND SHRCH|DAI|D</t>
+  </si>
+  <si>
+    <t>CHNCHAN BIMABIPATAPAJAMIM</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PDAPDAI|BBH|CH|J |PCH|AI|DAPDASHR|D YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PDAPDAI|BBH|CH|J |PCH|AI|DAPDASHR|D YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI SHRCH|T|BBH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI SHRCH|T|BBH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN DANEJAMCHIMIMK</t>
+  </si>
+  <si>
+    <t>CHNCHAN KIMAIM</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBHDYABBHDYASHRADYAKDYACH SHRCH|K|DACHSHRADYAK|AIBHT|CH AIBHTBBHDYAK THATHABHBBHDYASHRADYAK L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBHDYABBHDYASHRADYAKDYACH SHRCH|K|DACHSHRADYAK|AIBHT|CH AIBHTBBHDYAK THATHABHBBHDYASHRADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBHDYABBHDYASHRADYAKDYACH SHRCH|K|DACHSHRADYAK|AIBHT|CH AIBHTBBHDYAK THATHABHBBHDYASHRADYAK L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>SHRANIN AIBIVAVAS THAMSAPACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN |UMIMTAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN BIMKACHANAT</t>
+  </si>
+  <si>
+    <t>SHRCH|DAK|S|D BBHCHABBH|CH BBH|DABH|DAPDAJ YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>SHRCH|DAK|S|D BBHCHABBH|CH BBH|DABH|DAPDAJ YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHAMHAMIMT</t>
+  </si>
+  <si>
+    <t>CHNCHAN JPUMTAPACHANAT</t>
+  </si>
+  <si>
+    <t>SHRANIN AIBIVAVAS THAMEJAP</t>
+  </si>
+  <si>
+    <t>CHNCHAN THAMASUMDAPALAM</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|CH|PCH SHRCH|DAPCH|J|BBH|CH|J YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|CH|PCH SHRCH|DAPCH|J|BBH|CH|J YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>SHRANIN AIBIVAVAS AIMTAKAMECHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN AIMTAKAMECHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JTAPDAK|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JTAPDAK|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JDANBBH|CH|J YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JDANBBH|CH|J YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAMKIVACHANAT CHAVAN 1</t>
+  </si>
+  <si>
+    <t>CHNCHAN AIMKAMNASAP</t>
+  </si>
+  <si>
+    <t>CHNCHAN |UMIMT CHMJAJAP AIVANAJI</t>
+  </si>
+  <si>
+    <t>CHNCHAN KPAHAMTABIM</t>
+  </si>
+  <si>
+    <t>CHNCHAN NTAKAMPADAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN THIMASAMP</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DASHR|DAS|D</t>
+  </si>
+  <si>
+    <t>CHNCHAN TMAIMIM</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAVAJAPATAM</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCHAPCH|J|DACH|AI|CH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PDANDAJ|CH|BBH|CH|J YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PDANDAJ|CH|BBH|CH|J YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH J~NADYABBHDYAJ~NADYASHRCHADYAKDYASHRADYAK L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH J~NADYABBHDYAJ~NADYASHRCHADYAKDYASHRADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH J~NADYABBHDYAJ~NADYASHRCHADYAKDYASHRADYAK L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN AIMTAKAPASACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN JPATAMIPACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN THAMEUMD</t>
+  </si>
+  <si>
+    <t>CHNCHAN |UHIMJ</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRCH|K|CHK|SHRADYABBH L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRCH|K|CHK|SHRADYABBH L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRCH|K|CHK|SHRADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DABH|BBH|CH|J YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH THATHABHDYAK|THABHDYATHATHABHDYABBHDYASHR L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DABH|BBH|CH|J YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>SHRCH|DAK|S|D BBHCHABBH|CH BBH|DABH|BBH|CH|J</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J THAT|AI|AI|D|BH|D SHRCH|T|SHRANDAJ|CH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHK|SHR|D|J THAT|AI|AI|D|BH|D SHRCH|T|SHRANDAJ|CH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN THPATAVARACHANAT</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH THATHABHSHRADYAK|SHRCH|CHK|J~NADYATHATHABHDYABBHDYASHR L|THABHDYAK|BBHDYASHRADYATHATHABHDYABBHDYASHRADYAK|J~NAJ~NATHABH DYACHK|SHRCHADYAKDY AIBHTBBHDYAK THATHABHK|D</t>
+  </si>
+  <si>
+    <t>SHRAK|CHAK|J~NADYABBHDYAJ |PBBH J~NADYABBH SHRADYABBH THATHABHSHRADYAK|SHRCH|CHK|J~NADYATHATHABHDYABBHDYASHR L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>SHRAK|CHAK|J~NADYABBHDYAJ |PBBH J~NADYABBH SHRADYABBH THATHABHSHRADYAK|SHRCH|CHK|J~NADYATHATHABHDYABBHDYASHR L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN SMIMAMTAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAPATARAMCHANAT</t>
+  </si>
+  <si>
+    <t>BBH|BBH J~NADYABBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AIDYABBH J~NADYABBHDYASHRADYAJDYAK|THATHABHDYABBHDYASHR L|PDYAKDYACHBBHDYAK|J~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JBH|DACH|T|DAI|BBH|CH|J YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JBH|DACH|T|DAI|BBH|CH|J YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>AIBHTBBHDYAK|J~NADYAIDYAK THATHABHBBH|THATHABHDYABBH AIBHT|BBHDYAK|SHRCHADYAK|CHAK|SHRADYABBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHT|BBHDYAK|SHRCHADYAK|CHAK|SHRADYABBH L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHT|BBHDYAK|SHRCHADYAK|CHAK|SHRADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAMHATAMNASAP</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DABH|BBH|CH|J|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH THATHABHDYAK|THABHDYATHATHABHDYABBHDYASHRADYAK L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DABH|BBH|CH|J|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN LANATAMUM</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JBH|DAMSHR|DACH|J|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JBH|DAMSHR|DACH|J|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN BHMJINAP</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DABBHPDAJ|D|BBH|CH|J SHRCH|DAI|K|D YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DABBHPDAJ|D|BBH|CH|J SHRCH|DAI|K|D YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DATPDAJ|CH Y|D|J|ND SHRCH|D BBHCH|J|DAKKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCH|DAI|S|DAK|CH|BBH|CH|J</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBHDYAJDYASHRCHADYAK|SHRADYAK L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH AIBHTBBHDYAJDYASHRCHADYAK|SHRADYAK L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHIMJAJAMACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN LAMNATAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN DAMTAMHANACHANAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH SHRCHAPDAI|CH|AI|BBH|CH|J</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH BBH|JBH|CHKDYASHRCHADYAK L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH BBH|JBH|CHKDYASHRCHADYAK L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PDANDAJ|D YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH |PDANDAJ|D YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>SHRANIN AIBIVAVAS AIMUMTAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN LANATAHANARACHANAT</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI S|T|BBH|DAI|BBH|CH|J YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI S|T|BBH|DAI|BBH|CH|J YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMBIINUM</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THAPCH|K|SHR|DANDAK|BBH|CH|J YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THAPCH|K|SHR|DANDAK|BBH|CH|J YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN THAMEMDUMT</t>
+  </si>
+  <si>
+    <t>CHNCHAN |SAMUCHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN SVIMJAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN THIMKAMCHAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN TAPATACHANAT</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH JBH|THABHK|AIBHT|CHK|BBHDYASHRCHADYABBH THATHABHDYAK|CH SHRATHABHCHK|CHAK|J~N L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH JBH|THABHK|AIBHT|CHK|BBHDYASHRCHADYABBH THATHABHDYAK|CH SHRATHABHCHK|CHAK|J~N L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRATHABHDYABBHDYASHRCH|CHK|BBH L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRATHABHDYABBHDYASHRCH|CHK|BBH L|DAJDYABBHDYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRATHABHDYAK|SHRCHADYAK|DAK|SHRADYABBH L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH SHRATHABHDYAK|SHRCHADYAK|DAK|SHRADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JDANBBH|CH|J DYAMDAI|CH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH JDANBBH|CH|J DYAMDAI|CH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHAMU CHNCHAN TMUCHANAT |EMSAP</t>
+  </si>
+  <si>
+    <t>CHNCHAN |DAKAMNAT</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DAJ|DAN YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH THATHABHDYAK|SHRADYAK|CH L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH BBH|DAJ|DAN YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI SHRCH|CH|J|D|T|CH YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH|CHBBH DYACHJBH|CHJDYAJDY|P AIBHTBBHDYABBHDYASHRADYAKDYAJDYABBH L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI SHRCH|CH|J|D|T|CH YAMT|CH|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI SHRCH|CH|J|D|T|CH YAD|DAMSHR|KKBH YAK|T|J|SHRAPKKBH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI THABHDAT|DACH|AI|CH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH|CHBBH DYACHJBH|CHJDYAJDY|P JBH|THABHK|JDYAK|BBHDY|PDYABBH L|CHAK|DAIBHTDYAD J~NADYABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>AIBHT|CHAPCH |PTHAPT|T|AI THABHDAT|DACH|AI|CH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN BHMRAMNASAP</t>
+  </si>
+  <si>
+    <t>CHNCHAN JMKAKAPACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMIMKACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN CHMIMKACHANAT CHAMU THIMUMD</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THAPCH|AI|DAPDAJ YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH THAPCH|AI|DAPDAJ YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN BIPASAMIMT CHMAAM PUMTAMJ</t>
+  </si>
+  <si>
+    <t>LAMDAKIP PN BN BIPASAMIMT</t>
+  </si>
+  <si>
+    <t>CHNCHAN BHMTAPIMTACHANAT</t>
+  </si>
+  <si>
+    <t>CHNCHAN BIMNAMTAP</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH|CHBBH DYACHJBH|CHJDYAJDY|P SHRCH|BBHDYACHAK|SHRADYABBH L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH|CHBBH DYACHJBH|CHJDYAJDY|P SHRCH|BBHDYACHAK|SHRADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH|CHBBH DYACHJBH|CHJDYAJDY|P SHRCH|BBHDYACHAK|SHRADYABBH L|J~NADYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH|CHBBH DYACHJBH|CHJDYAJDY|P SHRCH|BBHDYACHAK|SHRADYABBH L|CHAK|DAIBHT D THATHABHDYAJDYASHRADYAIBHT|CHJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH K|DASHR|CHPCH YAD|DAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH|THATHABHDYABBH J~NADYAK|AIBHTDYABBHCHBBH L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>BBHCHABBH|CH K|DASHR|CHPCH YANDAMSHR|KKBH</t>
+  </si>
+  <si>
+    <t>CHNCHAN THAMBIIMTARAM</t>
+  </si>
+  <si>
+    <t>CHNCHAN AIMIKAMEI</t>
+  </si>
+  <si>
+    <t>CHNCHAN THIMKAMNATAM</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|KDYAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHABBHDYASHRCHADYASHRCHADY|PDYAKDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>THATHABHBBH BBH|BBH SHRADYABBHDYASHRCH|CHK|AIDYAK|PDYAK|AI KL|BBHDYASHRCHADYABBH L|CHAK|DAIBHTDYAJ~NAJ~NATHABH ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -557,8 +1403,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -574,7 +1428,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -582,12 +1436,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -886,76 +1758,139 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>441</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>442</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>443</v>
       </c>
       <c r="F2" t="s">
-        <v>162</v>
+        <v>444</v>
       </c>
       <c r="G2" t="s">
-        <v>163</v>
+        <v>445</v>
       </c>
       <c r="H2" t="s">
-        <v>164</v>
+        <v>446</v>
       </c>
       <c r="I2" t="s">
-        <v>165</v>
+        <v>447</v>
       </c>
       <c r="J2" t="s">
-        <v>166</v>
+        <v>448</v>
       </c>
       <c r="K2" t="s">
-        <v>167</v>
+        <v>449</v>
       </c>
       <c r="L2" t="s">
-        <v>168</v>
+        <v>450</v>
       </c>
       <c r="M2" t="s">
-        <v>169</v>
+        <v>451</v>
       </c>
       <c r="N2" t="s">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="O2" t="s">
-        <v>171</v>
+        <v>453</v>
       </c>
       <c r="P2" t="s">
-        <v>172</v>
+        <v>454</v>
       </c>
       <c r="Q2" t="s">
-        <v>173</v>
+        <v>455</v>
       </c>
       <c r="R2" t="s">
-        <v>174</v>
+        <v>456</v>
       </c>
       <c r="S2" t="s">
-        <v>175</v>
+        <v>457</v>
       </c>
       <c r="T2" t="s">
-        <v>176</v>
+        <v>458</v>
       </c>
       <c r="U2" t="s">
-        <v>177</v>
+        <v>459</v>
       </c>
       <c r="V2" t="s">
-        <v>178</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -963,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>945</v>
@@ -1031,7 +1966,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>972</v>
@@ -1099,7 +2034,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>580</v>
@@ -1167,7 +2102,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>943</v>
@@ -1235,7 +2170,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>1053</v>
@@ -1303,7 +2238,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>766</v>
@@ -1371,7 +2306,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>698</v>
@@ -1439,7 +2374,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>1139</v>
@@ -1507,7 +2442,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>1139</v>
@@ -1575,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>707</v>
@@ -1643,7 +2578,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>853</v>
@@ -1711,7 +2646,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>1079</v>
@@ -1779,7 +2714,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C15">
         <v>965</v>
@@ -1847,7 +2782,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>1046</v>
@@ -1915,7 +2850,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>739</v>
@@ -1983,7 +2918,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C18">
         <v>483</v>
@@ -2051,7 +2986,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>1115</v>
@@ -2119,7 +3054,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>1134</v>
@@ -2187,7 +3122,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>850</v>
@@ -2255,7 +3190,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C22">
         <v>846</v>
@@ -2323,7 +3258,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C23">
         <v>642</v>
@@ -2391,7 +3326,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C24">
         <v>652</v>
@@ -2459,7 +3394,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <v>610</v>
@@ -2527,7 +3462,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>627</v>
@@ -2595,7 +3530,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>631</v>
@@ -2663,7 +3598,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>611</v>
@@ -2731,7 +3666,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <v>778</v>
@@ -2799,7 +3734,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>812</v>
@@ -2867,7 +3802,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C31">
         <v>660</v>
@@ -2935,7 +3870,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <v>580</v>
@@ -3003,7 +3938,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C33">
         <v>725</v>
@@ -3071,7 +4006,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C34">
         <v>601</v>
@@ -3139,7 +4074,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C35">
         <v>1042</v>
@@ -3207,7 +4142,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C36">
         <v>935</v>
@@ -3275,7 +4210,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C37">
         <v>1050</v>
@@ -3343,7 +4278,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C38">
         <v>1085</v>
@@ -3411,7 +4346,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C39">
         <v>846</v>
@@ -3479,7 +4414,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="C40">
         <v>919</v>
@@ -3547,7 +4482,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C41">
         <v>960</v>
@@ -3615,7 +4550,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="C42">
         <v>721</v>
@@ -3683,7 +4618,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C43">
         <v>732</v>
@@ -3751,7 +4686,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C44">
         <v>1031</v>
@@ -3819,7 +4754,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <v>957</v>
@@ -3887,7 +4822,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="C46">
         <v>1153</v>
@@ -3955,7 +4890,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="C47">
         <v>827</v>
@@ -4023,7 +4958,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C48">
         <v>831</v>
@@ -4091,7 +5026,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C49">
         <v>1116</v>
@@ -4159,7 +5094,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C50">
         <v>1130</v>
@@ -4227,7 +5162,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="C51">
         <v>972</v>
@@ -4295,7 +5230,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="C52">
         <v>1142</v>
@@ -4363,7 +5298,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="C53">
         <v>1114</v>
@@ -4431,7 +5366,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="C54">
         <v>664</v>
@@ -4499,7 +5434,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <v>911</v>
@@ -4567,7 +5502,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="C56">
         <v>1029</v>
@@ -4635,7 +5570,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -4703,7 +5638,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <v>976</v>
@@ -4771,7 +5706,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="C59">
         <v>722</v>
@@ -4839,7 +5774,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="C60">
         <v>636</v>
@@ -4907,7 +5842,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="C61">
         <v>994</v>
@@ -4975,7 +5910,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="C62">
         <v>365</v>
@@ -5043,7 +5978,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="C63">
         <v>1160</v>
@@ -5111,7 +6046,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="C64">
         <v>1123</v>
@@ -5179,7 +6114,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C65">
         <v>1007</v>
@@ -5247,7 +6182,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="C66">
         <v>594</v>
@@ -5315,7 +6250,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="C67">
         <v>677</v>
@@ -5383,7 +6318,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="C68">
         <v>591</v>
@@ -5451,7 +6386,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="C69">
         <v>619</v>
@@ -5519,7 +6454,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C70">
         <v>573</v>
@@ -5587,7 +6522,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C71">
         <v>1084</v>
@@ -5655,7 +6590,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C72">
         <v>775</v>
@@ -5723,7 +6658,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C73">
         <v>742</v>
@@ -5791,7 +6726,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="C74">
         <v>621</v>
@@ -5859,7 +6794,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="C75">
         <v>568</v>
@@ -5927,7 +6862,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="C76">
         <v>543</v>
@@ -5995,7 +6930,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C77">
         <v>781</v>
@@ -6063,7 +6998,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C78">
         <v>822</v>
@@ -6131,7 +7066,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C79">
         <v>815</v>
@@ -6199,7 +7134,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="C80">
         <v>832</v>
@@ -6267,7 +7202,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="C81">
         <v>806</v>
@@ -6335,7 +7270,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="C82">
         <v>688</v>
@@ -6403,7 +7338,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="C83">
         <v>957</v>
@@ -6471,7 +7406,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="C84">
         <v>785</v>
@@ -6539,7 +7474,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="C85">
         <v>607</v>
@@ -6607,7 +7542,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="C86">
         <v>902</v>
@@ -6675,7 +7610,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C87">
         <v>487</v>
@@ -6743,7 +7678,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="C88">
         <v>619</v>
@@ -6811,7 +7746,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="C89">
         <v>646</v>
@@ -6879,7 +7814,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="C90">
         <v>683</v>
@@ -6947,7 +7882,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="C91">
         <v>583</v>
@@ -7015,7 +7950,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="C92">
         <v>1044</v>
@@ -7083,7 +8018,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="C93">
         <v>526</v>
@@ -7151,7 +8086,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="C94">
         <v>942</v>
@@ -7219,7 +8154,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="C95">
         <v>978</v>
@@ -7287,7 +8222,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="C96">
         <v>731</v>
@@ -7355,7 +8290,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="C97">
         <v>720</v>
@@ -7423,7 +8358,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="C98">
         <v>631</v>
@@ -7491,7 +8426,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C99">
         <v>562</v>
@@ -7559,7 +8494,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="C100">
         <v>737</v>
@@ -7627,7 +8562,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="C101">
         <v>732</v>
@@ -7695,7 +8630,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="C102">
         <v>1060</v>
@@ -7763,7 +8698,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="C103">
         <v>1039</v>
@@ -7831,7 +8766,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="C104">
         <v>719</v>
@@ -7899,7 +8834,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="C105">
         <v>598</v>
@@ -7967,7 +8902,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="C106">
         <v>576</v>
@@ -8035,7 +8970,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="C107">
         <v>424</v>
@@ -8103,7 +9038,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="C108">
         <v>1172</v>
@@ -8171,7 +9106,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="C109">
         <v>764</v>
@@ -8239,7 +9174,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="C110">
         <v>726</v>
@@ -8307,7 +9242,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="C111">
         <v>948</v>
@@ -8375,7 +9310,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="C112">
         <v>903</v>
@@ -8443,7 +9378,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="C113">
         <v>891</v>
@@ -8511,7 +9446,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C114">
         <v>912</v>
@@ -8579,7 +9514,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="C115">
         <v>1130</v>
@@ -8647,7 +9582,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="C116">
         <v>860</v>
@@ -8715,7 +9650,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="C117">
         <v>1143</v>
@@ -8783,7 +9718,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="C118">
         <v>727</v>
@@ -8851,7 +9786,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="C119">
         <v>615</v>
@@ -8919,7 +9854,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="C120">
         <v>1125</v>
@@ -8987,7 +9922,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="C121">
         <v>718</v>
@@ -9055,7 +9990,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="C122">
         <v>625</v>
@@ -9123,7 +10058,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="C123">
         <v>768</v>
@@ -9191,7 +10126,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="C124">
         <v>758</v>
@@ -9259,7 +10194,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="C125">
         <v>477</v>
@@ -9327,7 +10262,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="C126">
         <v>1044</v>
@@ -9395,7 +10330,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="C127">
         <v>727</v>
@@ -9463,7 +10398,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="C128">
         <v>580</v>
@@ -9531,7 +10466,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="C129">
         <v>674</v>
@@ -9599,7 +10534,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="C130">
         <v>644</v>
@@ -9667,7 +10602,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="C131">
         <v>803</v>
@@ -9735,7 +10670,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="C132">
         <v>693</v>
@@ -9803,7 +10738,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="C133">
         <v>1098</v>
@@ -9871,7 +10806,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="C134">
         <v>1015</v>
@@ -9939,7 +10874,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="C135">
         <v>936</v>
@@ -10007,7 +10942,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="C136">
         <v>712</v>
@@ -10075,7 +11010,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="C137">
         <v>761</v>
@@ -10143,7 +11078,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="C138">
         <v>835</v>
@@ -10211,7 +11146,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="C139">
         <v>1092</v>
@@ -10279,7 +11214,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="C140">
         <v>1095</v>
@@ -10347,7 +11282,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="C141">
         <v>785</v>
@@ -10415,7 +11350,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="C142">
         <v>773</v>
@@ -10483,7 +11418,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="C143">
         <v>1082</v>
@@ -10551,7 +11486,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="C144">
         <v>926</v>
@@ -10619,7 +11554,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="C145">
         <v>669</v>
@@ -10687,7 +11622,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="C146">
         <v>1043</v>
@@ -10755,7 +11690,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="C147">
         <v>703</v>
@@ -10823,7 +11758,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>674</v>
@@ -10891,7 +11826,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>573</v>
@@ -10959,7 +11894,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="C150">
         <v>928</v>
@@ -11027,7 +11962,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="C151">
         <v>1109</v>
@@ -11095,7 +12030,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="C152">
         <v>1080</v>
@@ -11163,7 +12098,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="C153">
         <v>633</v>
@@ -11231,7 +12166,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="C154">
         <v>565</v>
@@ -11299,7 +12234,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="C155">
         <v>1110</v>
@@ -11367,7 +12302,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="C156">
         <v>1110</v>
@@ -11435,7 +12370,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="C157">
         <v>1042</v>
@@ -11503,7 +12438,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="C158">
         <v>1027</v>
@@ -11571,7 +12506,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="C159">
         <v>1041</v>
@@ -11639,7 +12574,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="C160">
         <v>927</v>
@@ -11707,7 +12642,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="C161">
         <v>853</v>
@@ -11775,7 +12710,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="C162">
         <v>865</v>
@@ -11843,7 +12778,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="C163">
         <v>1022</v>
@@ -11911,7 +12846,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="C164">
         <v>1050</v>
@@ -11979,7 +12914,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="C165">
         <v>850</v>
@@ -12047,7 +12982,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="C166">
         <v>990</v>
@@ -12115,7 +13050,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="C167">
         <v>953</v>
@@ -12183,7 +13118,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="C168">
         <v>873</v>
@@ -12251,7 +13186,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="C169">
         <v>1122</v>
@@ -12319,7 +13254,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>83</v>
+        <v>188</v>
       </c>
       <c r="C170">
         <v>795</v>
@@ -12387,7 +13322,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="C171">
         <v>739</v>
@@ -12455,7 +13390,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="C172">
         <v>1126</v>
@@ -12523,7 +13458,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="C173">
         <v>759</v>
@@ -12591,7 +13526,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="C174">
         <v>1155</v>
@@ -12659,7 +13594,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>43</v>
+        <v>193</v>
       </c>
       <c r="C175">
         <v>989</v>
@@ -12727,7 +13662,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="C176">
         <v>1056</v>
@@ -12795,7 +13730,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>43</v>
+        <v>195</v>
       </c>
       <c r="C177">
         <v>884</v>
@@ -12863,7 +13798,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>43</v>
+        <v>196</v>
       </c>
       <c r="C178">
         <v>1152</v>
@@ -12931,7 +13866,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="C179">
         <v>671</v>
@@ -12999,7 +13934,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="C180">
         <v>611</v>
@@ -13067,7 +14002,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="C181">
         <v>1057</v>
@@ -13135,7 +14070,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="C182">
         <v>1054</v>
@@ -13203,7 +14138,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="C183">
         <v>1172</v>
@@ -13271,7 +14206,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="C184">
         <v>1163</v>
@@ -13339,7 +14274,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="C185">
         <v>1182</v>
@@ -13407,7 +14342,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
       <c r="C186">
         <v>673</v>
@@ -13475,7 +14410,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="C187">
         <v>578</v>
@@ -13543,7 +14478,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>90</v>
+        <v>206</v>
       </c>
       <c r="C188">
         <v>745</v>
@@ -13611,7 +14546,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="C189">
         <v>759</v>
@@ -13679,7 +14614,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>92</v>
+        <v>208</v>
       </c>
       <c r="C190">
         <v>770</v>
@@ -13747,7 +14682,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="C191">
         <v>1088</v>
@@ -13815,7 +14750,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="C192">
         <v>785</v>
@@ -13883,7 +14818,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>48</v>
+        <v>211</v>
       </c>
       <c r="C193">
         <v>523</v>
@@ -13951,7 +14886,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="C194">
         <v>1006</v>
@@ -14019,7 +14954,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>7</v>
+        <v>213</v>
       </c>
       <c r="C195">
         <v>1024</v>
@@ -14087,7 +15022,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="C196">
         <v>909</v>
@@ -14155,7 +15090,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>48</v>
+        <v>215</v>
       </c>
       <c r="C197">
         <v>415</v>
@@ -14223,7 +15158,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="C198">
         <v>1062</v>
@@ -14291,7 +15226,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>60</v>
+        <v>217</v>
       </c>
       <c r="C199">
         <v>974</v>
@@ -14359,7 +15294,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>60</v>
+        <v>218</v>
       </c>
       <c r="C200">
         <v>939</v>
@@ -14427,7 +15362,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>95</v>
+        <v>219</v>
       </c>
       <c r="C201">
         <v>1098</v>
@@ -14495,7 +15430,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="C202">
         <v>1001</v>
@@ -14563,7 +15498,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>59</v>
+        <v>221</v>
       </c>
       <c r="C203">
         <v>974</v>
@@ -14631,7 +15566,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>60</v>
+        <v>222</v>
       </c>
       <c r="C204">
         <v>844</v>
@@ -14699,7 +15634,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>96</v>
+        <v>223</v>
       </c>
       <c r="C205">
         <v>715</v>
@@ -14767,7 +15702,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>12</v>
+        <v>224</v>
       </c>
       <c r="C206">
         <v>1019</v>
@@ -14835,7 +15770,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>13</v>
+        <v>225</v>
       </c>
       <c r="C207">
         <v>959</v>
@@ -14903,7 +15838,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="C208">
         <v>693</v>
@@ -14971,7 +15906,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="C209">
         <v>784</v>
@@ -15039,7 +15974,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>97</v>
+        <v>228</v>
       </c>
       <c r="C210">
         <v>618</v>
@@ -15107,7 +16042,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>98</v>
+        <v>229</v>
       </c>
       <c r="C211">
         <v>652</v>
@@ -15175,7 +16110,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="C212">
         <v>803</v>
@@ -15243,7 +16178,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="C213">
         <v>1050</v>
@@ -15311,7 +16246,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="C214">
         <v>1128</v>
@@ -15379,7 +16314,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>40</v>
+        <v>233</v>
       </c>
       <c r="C215">
         <v>527</v>
@@ -15447,7 +16382,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>41</v>
+        <v>234</v>
       </c>
       <c r="C216">
         <v>682</v>
@@ -15515,7 +16450,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>72</v>
+        <v>235</v>
       </c>
       <c r="C217">
         <v>1059</v>
@@ -15583,7 +16518,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>7</v>
+        <v>236</v>
       </c>
       <c r="C218">
         <v>745</v>
@@ -15651,7 +16586,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>73</v>
+        <v>237</v>
       </c>
       <c r="C219">
         <v>1143</v>
@@ -15719,7 +16654,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>101</v>
+        <v>238</v>
       </c>
       <c r="C220">
         <v>988</v>
@@ -15787,7 +16722,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>97</v>
+        <v>239</v>
       </c>
       <c r="C221">
         <v>1039</v>
@@ -15855,7 +16790,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>102</v>
+        <v>240</v>
       </c>
       <c r="C222">
         <v>989</v>
@@ -15923,7 +16858,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="C223">
         <v>1015</v>
@@ -15991,7 +16926,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>56</v>
+        <v>242</v>
       </c>
       <c r="C224">
         <v>1099</v>
@@ -16059,7 +16994,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>51</v>
+        <v>243</v>
       </c>
       <c r="C225">
         <v>708</v>
@@ -16127,7 +17062,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>103</v>
+        <v>244</v>
       </c>
       <c r="C226">
         <v>738</v>
@@ -16195,7 +17130,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>104</v>
+        <v>245</v>
       </c>
       <c r="C227">
         <v>622</v>
@@ -16263,7 +17198,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>25</v>
+        <v>246</v>
       </c>
       <c r="C228">
         <v>821</v>
@@ -16331,7 +17266,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>26</v>
+        <v>247</v>
       </c>
       <c r="C229">
         <v>686</v>
@@ -16399,7 +17334,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="C230">
         <v>1108</v>
@@ -16467,7 +17402,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="C231">
         <v>646</v>
@@ -16535,7 +17470,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="C232">
         <v>783</v>
@@ -16603,7 +17538,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>107</v>
+        <v>251</v>
       </c>
       <c r="C233">
         <v>949</v>
@@ -16671,7 +17606,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="C234">
         <v>944</v>
@@ -16739,7 +17674,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="C235">
         <v>605</v>
@@ -16807,7 +17742,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="C236">
         <v>559</v>
@@ -16875,7 +17810,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>109</v>
+        <v>253</v>
       </c>
       <c r="C237">
         <v>594</v>
@@ -16943,7 +17878,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>110</v>
+        <v>254</v>
       </c>
       <c r="C238">
         <v>584</v>
@@ -17011,7 +17946,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>111</v>
+        <v>255</v>
       </c>
       <c r="C239">
         <v>726</v>
@@ -17079,7 +18014,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>112</v>
+        <v>256</v>
       </c>
       <c r="C240">
         <v>697</v>
@@ -17147,7 +18082,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>113</v>
+        <v>257</v>
       </c>
       <c r="C241">
         <v>892</v>
@@ -17215,7 +18150,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>36</v>
+        <v>258</v>
       </c>
       <c r="C242">
         <v>477</v>
@@ -17283,7 +18218,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>114</v>
+        <v>259</v>
       </c>
       <c r="C243">
         <v>892</v>
@@ -17351,7 +18286,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>114</v>
+        <v>260</v>
       </c>
       <c r="C244">
         <v>765</v>
@@ -17419,7 +18354,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>115</v>
+        <v>261</v>
       </c>
       <c r="C245">
         <v>1046</v>
@@ -17487,7 +18422,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>116</v>
+        <v>262</v>
       </c>
       <c r="C246">
         <v>1076</v>
@@ -17555,7 +18490,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>117</v>
+        <v>263</v>
       </c>
       <c r="C247">
         <v>772</v>
@@ -17623,7 +18558,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="C248">
         <v>809</v>
@@ -17691,7 +18626,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="C249">
         <v>612</v>
@@ -17759,7 +18694,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="C250">
         <v>1130</v>
@@ -17827,7 +18762,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="C251">
         <v>1138</v>
@@ -17895,7 +18830,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>119</v>
+        <v>268</v>
       </c>
       <c r="C252">
         <v>1061</v>
@@ -17963,7 +18898,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>120</v>
+        <v>269</v>
       </c>
       <c r="C253">
         <v>929</v>
@@ -18031,7 +18966,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>17</v>
+        <v>270</v>
       </c>
       <c r="C254">
         <v>577</v>
@@ -18099,7 +19034,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>18</v>
+        <v>271</v>
       </c>
       <c r="C255">
         <v>670</v>
@@ -18167,7 +19102,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>55</v>
+        <v>272</v>
       </c>
       <c r="C256">
         <v>453</v>
@@ -18235,7 +19170,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>86</v>
+        <v>273</v>
       </c>
       <c r="C257">
         <v>989</v>
@@ -18303,7 +19238,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>87</v>
+        <v>274</v>
       </c>
       <c r="C258">
         <v>912</v>
@@ -18371,7 +19306,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>73</v>
+        <v>275</v>
       </c>
       <c r="C259">
         <v>718</v>
@@ -18439,7 +19374,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>27</v>
+        <v>276</v>
       </c>
       <c r="C260">
         <v>463</v>
@@ -18507,7 +19442,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>121</v>
+        <v>277</v>
       </c>
       <c r="C261">
         <v>798</v>
@@ -18575,7 +19510,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>95</v>
+        <v>278</v>
       </c>
       <c r="C262">
         <v>500</v>
@@ -18643,7 +19578,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>37</v>
+        <v>279</v>
       </c>
       <c r="C263">
         <v>672</v>
@@ -18711,7 +19646,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>37</v>
+        <v>280</v>
       </c>
       <c r="C264">
         <v>647</v>
@@ -18779,7 +19714,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>37</v>
+        <v>281</v>
       </c>
       <c r="C265">
         <v>1133</v>
@@ -18847,7 +19782,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>94</v>
+        <v>282</v>
       </c>
       <c r="C266">
         <v>1088</v>
@@ -18915,7 +19850,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>7</v>
+        <v>283</v>
       </c>
       <c r="C267">
         <v>1098</v>
@@ -18983,7 +19918,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>14</v>
+        <v>284</v>
       </c>
       <c r="C268">
         <v>897</v>
@@ -19051,7 +19986,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="C269">
         <v>881</v>
@@ -19119,7 +20054,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="C270">
         <v>1098</v>
@@ -19187,7 +20122,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>60</v>
+        <v>286</v>
       </c>
       <c r="C271">
         <v>1075</v>
@@ -19255,7 +20190,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>122</v>
+        <v>287</v>
       </c>
       <c r="C272">
         <v>767</v>
@@ -19323,7 +20258,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>123</v>
+        <v>288</v>
       </c>
       <c r="C273">
         <v>793</v>
@@ -19391,7 +20326,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>33</v>
+        <v>289</v>
       </c>
       <c r="C274">
         <v>930</v>
@@ -19459,7 +20394,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>124</v>
+        <v>290</v>
       </c>
       <c r="C275">
         <v>654</v>
@@ -19527,7 +20462,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>125</v>
+        <v>291</v>
       </c>
       <c r="C276">
         <v>615</v>
@@ -19595,7 +20530,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>55</v>
+        <v>292</v>
       </c>
       <c r="C277">
         <v>806</v>
@@ -19663,7 +20598,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>59</v>
+        <v>293</v>
       </c>
       <c r="C278">
         <v>627</v>
@@ -19731,7 +20666,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>60</v>
+        <v>294</v>
       </c>
       <c r="C279">
         <v>666</v>
@@ -19799,7 +20734,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>33</v>
+        <v>295</v>
       </c>
       <c r="C280">
         <v>517</v>
@@ -19867,7 +20802,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>73</v>
+        <v>296</v>
       </c>
       <c r="C281">
         <v>694</v>
@@ -19935,7 +20870,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>56</v>
+        <v>297</v>
       </c>
       <c r="C282">
         <v>617</v>
@@ -20003,7 +20938,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>44</v>
+        <v>298</v>
       </c>
       <c r="C283">
         <v>725</v>
@@ -20071,7 +21006,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="C284">
         <v>761</v>
@@ -20139,7 +21074,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>45</v>
+        <v>300</v>
       </c>
       <c r="C285">
         <v>983</v>
@@ -20207,7 +21142,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>59</v>
+        <v>301</v>
       </c>
       <c r="C286">
         <v>709</v>
@@ -20275,7 +21210,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>60</v>
+        <v>302</v>
       </c>
       <c r="C287">
         <v>675</v>
@@ -20343,7 +21278,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>55</v>
+        <v>303</v>
       </c>
       <c r="C288">
         <v>1049</v>
@@ -20411,7 +21346,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>57</v>
+        <v>304</v>
       </c>
       <c r="C289">
         <v>865</v>
@@ -20479,7 +21414,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>58</v>
+        <v>305</v>
       </c>
       <c r="C290">
         <v>1015</v>
@@ -20547,7 +21482,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>59</v>
+        <v>306</v>
       </c>
       <c r="C291">
         <v>1154</v>
@@ -20615,7 +21550,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>60</v>
+        <v>307</v>
       </c>
       <c r="C292">
         <v>1041</v>
@@ -20683,7 +21618,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>60</v>
+        <v>308</v>
       </c>
       <c r="C293">
         <v>1149</v>
@@ -20751,7 +21686,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>27</v>
+        <v>309</v>
       </c>
       <c r="C294">
         <v>454</v>
@@ -20819,7 +21754,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>27</v>
+        <v>310</v>
       </c>
       <c r="C295">
         <v>773</v>
@@ -20887,7 +21822,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>55</v>
+        <v>311</v>
       </c>
       <c r="C296">
         <v>896</v>
@@ -20955,7 +21890,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>33</v>
+        <v>312</v>
       </c>
       <c r="C297">
         <v>822</v>
@@ -21023,7 +21958,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>14</v>
+        <v>313</v>
       </c>
       <c r="C298">
         <v>1081</v>
@@ -21091,7 +22026,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>15</v>
+        <v>314</v>
       </c>
       <c r="C299">
         <v>1020</v>
@@ -21159,7 +22094,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>15</v>
+        <v>315</v>
       </c>
       <c r="C300">
         <v>979</v>
@@ -21227,7 +22162,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C301">
         <v>891</v>
@@ -21295,7 +22230,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>31</v>
+        <v>316</v>
       </c>
       <c r="C302">
         <v>747</v>
@@ -21363,7 +22298,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>32</v>
+        <v>317</v>
       </c>
       <c r="C303">
         <v>1175</v>
@@ -21431,7 +22366,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>32</v>
+        <v>318</v>
       </c>
       <c r="C304">
         <v>1080</v>
@@ -21499,7 +22434,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>32</v>
+        <v>319</v>
       </c>
       <c r="C305">
         <v>1035</v>
@@ -21567,7 +22502,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>126</v>
+        <v>320</v>
       </c>
       <c r="C306">
         <v>791</v>
@@ -21635,7 +22570,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>127</v>
+        <v>321</v>
       </c>
       <c r="C307">
         <v>615</v>
@@ -21703,7 +22638,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>128</v>
+        <v>322</v>
       </c>
       <c r="C308">
         <v>650</v>
@@ -21771,7 +22706,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>128</v>
+        <v>323</v>
       </c>
       <c r="C309">
         <v>621</v>
@@ -21839,7 +22774,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>94</v>
+        <v>324</v>
       </c>
       <c r="C310">
         <v>1071</v>
@@ -21907,7 +22842,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>129</v>
+        <v>325</v>
       </c>
       <c r="C311">
         <v>815</v>
@@ -21975,7 +22910,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>130</v>
+        <v>326</v>
       </c>
       <c r="C312">
         <v>1135</v>
@@ -22043,7 +22978,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>130</v>
+        <v>327</v>
       </c>
       <c r="C313">
         <v>1146</v>
@@ -22111,7 +23046,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>33</v>
+        <v>328</v>
       </c>
       <c r="C314">
         <v>895</v>
@@ -22179,7 +23114,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="C315">
         <v>654</v>
@@ -22247,7 +23182,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="C316">
         <v>650</v>
@@ -22315,7 +23250,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>133</v>
+        <v>331</v>
       </c>
       <c r="C317">
         <v>721</v>
@@ -22383,7 +23318,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>134</v>
+        <v>332</v>
       </c>
       <c r="C318">
         <v>546</v>
@@ -22451,7 +23386,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>135</v>
+        <v>333</v>
       </c>
       <c r="C319">
         <v>768</v>
@@ -22519,7 +23454,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>10</v>
+        <v>334</v>
       </c>
       <c r="C320">
         <v>605</v>
@@ -22587,7 +23522,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>10</v>
+        <v>335</v>
       </c>
       <c r="C321">
         <v>1087</v>
@@ -22655,7 +23590,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>136</v>
+        <v>336</v>
       </c>
       <c r="C322">
         <v>689</v>
@@ -22723,7 +23658,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>137</v>
+        <v>337</v>
       </c>
       <c r="C323">
         <v>579</v>
@@ -22791,7 +23726,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>131</v>
+        <v>337</v>
       </c>
       <c r="C324">
         <v>1164</v>
@@ -22859,7 +23794,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="C325">
         <v>1140</v>
@@ -22927,7 +23862,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>48</v>
+        <v>339</v>
       </c>
       <c r="C326">
         <v>522</v>
@@ -22995,7 +23930,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>55</v>
+        <v>340</v>
       </c>
       <c r="C327">
         <v>1020</v>
@@ -23063,7 +23998,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>31</v>
+        <v>341</v>
       </c>
       <c r="C328">
         <v>649</v>
@@ -23131,7 +24066,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>32</v>
+        <v>342</v>
       </c>
       <c r="C329">
         <v>613</v>
@@ -23199,7 +24134,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>32</v>
+        <v>343</v>
       </c>
       <c r="C330">
         <v>1143</v>
@@ -23267,7 +24202,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>32</v>
+        <v>344</v>
       </c>
       <c r="C331">
         <v>1081</v>
@@ -23335,7 +24270,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>33</v>
+        <v>345</v>
       </c>
       <c r="C332">
         <v>1068</v>
@@ -23403,7 +24338,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>57</v>
+        <v>346</v>
       </c>
       <c r="C333">
         <v>825</v>
@@ -23471,7 +24406,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>58</v>
+        <v>347</v>
       </c>
       <c r="C334">
         <v>908</v>
@@ -23539,7 +24474,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>73</v>
+        <v>348</v>
       </c>
       <c r="C335">
         <v>634</v>
@@ -23607,7 +24542,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>138</v>
+        <v>349</v>
       </c>
       <c r="C336">
         <v>784</v>
@@ -23675,7 +24610,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>138</v>
+        <v>350</v>
       </c>
       <c r="C337">
         <v>555</v>
@@ -23743,7 +24678,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>139</v>
+        <v>351</v>
       </c>
       <c r="C338">
         <v>1135</v>
@@ -23811,7 +24746,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
       <c r="C339">
         <v>919</v>
@@ -23879,7 +24814,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>17</v>
+        <v>353</v>
       </c>
       <c r="C340">
         <v>1051</v>
@@ -23947,7 +24882,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>18</v>
+        <v>354</v>
       </c>
       <c r="C341">
         <v>1111</v>
@@ -24015,7 +24950,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>7</v>
+        <v>355</v>
       </c>
       <c r="C342">
         <v>909</v>
@@ -24083,7 +25018,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>25</v>
+        <v>356</v>
       </c>
       <c r="C343">
         <v>818</v>
@@ -24151,7 +25086,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>26</v>
+        <v>357</v>
       </c>
       <c r="C344">
         <v>682</v>
@@ -24219,7 +25154,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>48</v>
+        <v>358</v>
       </c>
       <c r="C345">
         <v>1098</v>
@@ -24287,7 +25222,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>57</v>
+        <v>359</v>
       </c>
       <c r="C346">
         <v>651</v>
@@ -24355,7 +25290,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>58</v>
+        <v>360</v>
       </c>
       <c r="C347">
         <v>611</v>
@@ -24423,7 +25358,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>17</v>
+        <v>361</v>
       </c>
       <c r="C348">
         <v>1156</v>
@@ -24491,7 +25426,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>18</v>
+        <v>362</v>
       </c>
       <c r="C349">
         <v>1032</v>
@@ -24559,7 +25494,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>42</v>
+        <v>363</v>
       </c>
       <c r="C350">
         <v>715</v>
@@ -24627,7 +25562,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>43</v>
+        <v>364</v>
       </c>
       <c r="C351">
         <v>645</v>
@@ -24695,7 +25630,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>43</v>
+        <v>365</v>
       </c>
       <c r="C352">
         <v>612</v>
@@ -24763,7 +25698,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>43</v>
+        <v>366</v>
       </c>
       <c r="C353">
         <v>616</v>
@@ -24831,7 +25766,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>43</v>
+        <v>367</v>
       </c>
       <c r="C354">
         <v>1125</v>
@@ -24899,7 +25834,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>27</v>
+        <v>368</v>
       </c>
       <c r="C355">
         <v>1016</v>
@@ -24967,7 +25902,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>140</v>
+        <v>369</v>
       </c>
       <c r="C356">
         <v>1186</v>
@@ -25035,7 +25970,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>140</v>
+        <v>370</v>
       </c>
       <c r="C357">
         <v>1042</v>
@@ -25103,7 +26038,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>33</v>
+        <v>371</v>
       </c>
       <c r="C358">
         <v>956</v>
@@ -25171,7 +26106,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>141</v>
+        <v>372</v>
       </c>
       <c r="C359">
         <v>947</v>
@@ -25239,7 +26174,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>142</v>
+        <v>373</v>
       </c>
       <c r="C360">
         <v>881</v>
@@ -25307,7 +26242,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>143</v>
+        <v>374</v>
       </c>
       <c r="C361">
         <v>751</v>
@@ -25375,7 +26310,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>55</v>
+        <v>375</v>
       </c>
       <c r="C362">
         <v>541</v>
@@ -25443,7 +26378,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>27</v>
+        <v>376</v>
       </c>
       <c r="C363">
         <v>939</v>
@@ -25511,7 +26446,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>33</v>
+        <v>377</v>
       </c>
       <c r="C364">
         <v>638</v>
@@ -25579,7 +26514,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>144</v>
+        <v>378</v>
       </c>
       <c r="C365">
         <v>710</v>
@@ -25647,7 +26582,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>59</v>
+        <v>379</v>
       </c>
       <c r="C366">
         <v>511</v>
@@ -25715,7 +26650,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="C367">
         <v>727</v>
@@ -25783,7 +26718,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>18</v>
+        <v>381</v>
       </c>
       <c r="C368">
         <v>740</v>
@@ -25851,7 +26786,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>17</v>
+        <v>382</v>
       </c>
       <c r="C369">
         <v>575</v>
@@ -25919,7 +26854,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>18</v>
+        <v>383</v>
       </c>
       <c r="C370">
         <v>854</v>
@@ -25987,7 +26922,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>18</v>
+        <v>384</v>
       </c>
       <c r="C371">
         <v>667</v>
@@ -26055,7 +26990,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>43</v>
+        <v>385</v>
       </c>
       <c r="C372">
         <v>1150</v>
@@ -26123,7 +27058,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>43</v>
+        <v>386</v>
       </c>
       <c r="C373">
         <v>852</v>
@@ -26191,7 +27126,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>43</v>
+        <v>387</v>
       </c>
       <c r="C374">
         <v>767</v>
@@ -26259,7 +27194,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>14</v>
+        <v>388</v>
       </c>
       <c r="C375">
         <v>659</v>
@@ -26327,7 +27262,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>15</v>
+        <v>389</v>
       </c>
       <c r="C376">
         <v>649</v>
@@ -26395,7 +27330,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>15</v>
+        <v>390</v>
       </c>
       <c r="C377">
         <v>649</v>
@@ -26463,7 +27398,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>48</v>
+        <v>391</v>
       </c>
       <c r="C378">
         <v>1065</v>
@@ -26531,7 +27466,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>145</v>
+        <v>392</v>
       </c>
       <c r="C379">
         <v>1097</v>
@@ -26599,7 +27534,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>146</v>
+        <v>393</v>
       </c>
       <c r="C380">
         <v>831</v>
@@ -26667,7 +27602,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>147</v>
+        <v>394</v>
       </c>
       <c r="C381">
         <v>789</v>
@@ -26735,7 +27670,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>31</v>
+        <v>395</v>
       </c>
       <c r="C382">
         <v>640</v>
@@ -26803,7 +27738,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>32</v>
+        <v>396</v>
       </c>
       <c r="C383">
         <v>623</v>
@@ -26871,7 +27806,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>43</v>
+        <v>397</v>
       </c>
       <c r="C384">
         <v>1162</v>
@@ -26939,7 +27874,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>42</v>
+        <v>398</v>
       </c>
       <c r="C385">
         <v>1059</v>
@@ -27007,7 +27942,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="C386">
         <v>1018</v>
@@ -27075,7 +28010,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>43</v>
+        <v>400</v>
       </c>
       <c r="C387">
         <v>1139</v>
@@ -27143,7 +28078,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>148</v>
+        <v>401</v>
       </c>
       <c r="C388">
         <v>1061</v>
@@ -27211,7 +28146,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>148</v>
+        <v>402</v>
       </c>
       <c r="C389">
         <v>933</v>
@@ -27279,7 +28214,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>149</v>
+        <v>403</v>
       </c>
       <c r="C390">
         <v>690</v>
@@ -27347,7 +28282,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>148</v>
+        <v>404</v>
       </c>
       <c r="C391">
         <v>636</v>
@@ -27415,7 +28350,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>150</v>
+        <v>405</v>
       </c>
       <c r="C392">
         <v>1067</v>
@@ -27483,7 +28418,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
       <c r="C393">
         <v>540</v>
@@ -27551,7 +28486,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>121</v>
+        <v>407</v>
       </c>
       <c r="C394">
         <v>1123</v>
@@ -27619,7 +28554,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>95</v>
+        <v>408</v>
       </c>
       <c r="C395">
         <v>1086</v>
@@ -27687,7 +28622,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>95</v>
+        <v>409</v>
       </c>
       <c r="C396">
         <v>637</v>
@@ -27755,7 +28690,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>95</v>
+        <v>410</v>
       </c>
       <c r="C397">
         <v>588</v>
@@ -27823,7 +28758,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>14</v>
+        <v>411</v>
       </c>
       <c r="C398">
         <v>632</v>
@@ -27891,7 +28826,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="C399">
         <v>628</v>
@@ -27959,7 +28894,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>15</v>
+        <v>413</v>
       </c>
       <c r="C400">
         <v>792</v>
@@ -28027,7 +28962,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>57</v>
+        <v>414</v>
       </c>
       <c r="C401">
         <v>639</v>
@@ -28095,7 +29030,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>58</v>
+        <v>415</v>
       </c>
       <c r="C402">
         <v>596</v>
@@ -28163,7 +29098,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>72</v>
+        <v>416</v>
       </c>
       <c r="C403">
         <v>952</v>
@@ -28231,7 +29166,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>152</v>
+        <v>417</v>
       </c>
       <c r="C404">
         <v>511</v>
@@ -28299,7 +29234,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>153</v>
+        <v>418</v>
       </c>
       <c r="C405">
         <v>832</v>
@@ -28367,7 +29302,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>154</v>
+        <v>419</v>
       </c>
       <c r="C406">
         <v>958</v>
@@ -28435,7 +29370,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>154</v>
+        <v>420</v>
       </c>
       <c r="C407">
         <v>694</v>
@@ -28503,7 +29438,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>154</v>
+        <v>421</v>
       </c>
       <c r="C408">
         <v>560</v>
@@ -28571,7 +29506,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>155</v>
+        <v>422</v>
       </c>
       <c r="C409">
         <v>601</v>
@@ -28639,7 +29574,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>7</v>
+        <v>423</v>
       </c>
       <c r="C410">
         <v>554</v>
@@ -28707,7 +29642,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>143</v>
+        <v>424</v>
       </c>
       <c r="C411">
         <v>680</v>
@@ -28775,7 +29710,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>17</v>
+        <v>425</v>
       </c>
       <c r="C412">
         <v>778</v>
@@ -28843,7 +29778,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>18</v>
+        <v>426</v>
       </c>
       <c r="C413">
         <v>633</v>
@@ -28911,7 +29846,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>18</v>
+        <v>427</v>
       </c>
       <c r="C414">
         <v>1086</v>
@@ -28979,7 +29914,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>18</v>
+        <v>428</v>
       </c>
       <c r="C415">
         <v>1109</v>
@@ -29047,7 +29982,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>156</v>
+        <v>429</v>
       </c>
       <c r="C416">
         <v>898</v>
@@ -29115,7 +30050,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>14</v>
+        <v>430</v>
       </c>
       <c r="C417">
         <v>692</v>
@@ -29183,7 +30118,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>15</v>
+        <v>431</v>
       </c>
       <c r="C418">
         <v>774</v>
@@ -29251,7 +30186,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>15</v>
+        <v>432</v>
       </c>
       <c r="C419">
         <v>1096</v>
@@ -29319,7 +30254,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>33</v>
+        <v>433</v>
       </c>
       <c r="C420">
         <v>475</v>
@@ -29387,7 +30322,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>33</v>
+        <v>434</v>
       </c>
       <c r="C421">
         <v>1031</v>
@@ -29455,7 +30390,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>33</v>
+        <v>435</v>
       </c>
       <c r="C422">
         <v>688</v>
@@ -29523,7 +30458,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>157</v>
+        <v>436</v>
       </c>
       <c r="C423">
         <v>709</v>
@@ -29591,7 +30526,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>158</v>
+        <v>437</v>
       </c>
       <c r="C424">
         <v>585</v>
@@ -29659,7 +30594,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>158</v>
+        <v>438</v>
       </c>
       <c r="C425">
         <v>1071</v>
@@ -29727,7 +30662,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>158</v>
+        <v>439</v>
       </c>
       <c r="C426">
         <v>629</v>
@@ -29795,7 +30730,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>158</v>
+        <v>440</v>
       </c>
       <c r="C427">
         <v>536</v>
